--- a/output/pdf_financials_xlsx/TRS.xlsx
+++ b/output/pdf_financials_xlsx/TRS.xlsx
@@ -6166,13 +6166,13 @@
         <v>0</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.272453</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0.062953</v>
+        <v>2.335406</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0.072397</v>
+        <v>2.34485</v>
       </c>
     </row>
     <row r="93">
@@ -7665,52 +7665,52 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.28445</v>
+        <v>-0.8682260000000001</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.604837</v>
+        <v>-2.009522</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.848758</v>
+        <v>-0.025206</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.3</v>
+        <v>0.165894</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.049974</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.091559</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.120439</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.259643</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.158517</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.001024</v>
+        <v>-0.347587</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.490677</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.482232</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.127257</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.062189</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0.01253</v>
+        <v>-0.042525</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0.327823</v>
+        <v>0.312223</v>
       </c>
     </row>
     <row r="119">
@@ -10290,7 +10290,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11546,7 +11550,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -20876,7 +20884,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TRS.xlsx
+++ b/output/pdf_financials_xlsx/TRS.xlsx
@@ -1059,28 +1059,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.045393</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.067383</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.086482</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003134</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001138</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000463</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000136</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>3.5e-05</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1101,16 +1101,16 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.005321</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.005064</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.001297</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.000243</v>
       </c>
     </row>
     <row r="13">
@@ -2066,28 +2066,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.181853</v>
+        <v>-1.227246</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.981457</v>
+        <v>-4.04884</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.710261</v>
+        <v>-1.796743</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.975394</v>
+        <v>-0.978528</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.099797</v>
+        <v>-1.100935</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.549926</v>
+        <v>-0.550389</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.1814</v>
+        <v>-0.181536</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.159945</v>
+        <v>-0.15998</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.191482</v>
@@ -2108,16 +2108,16 @@
         <v>-0.227622</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.331425</v>
+        <v>0.326104</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.233692</v>
+        <v>-0.238756</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.166144</v>
+        <v>-0.167441</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.460389</v>
+        <v>-0.460632</v>
       </c>
     </row>
     <row r="28">
@@ -2188,28 +2188,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.181853</v>
+        <v>-1.227246</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.981457</v>
+        <v>-4.04884</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.70395</v>
+        <v>-1.790432</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.970127</v>
+        <v>-0.973261</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.095745</v>
+        <v>-1.096883</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.5473209999999999</v>
+        <v>-0.547784</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.1814</v>
+        <v>-0.181536</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.159945</v>
+        <v>-0.15998</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.191482</v>
@@ -2230,16 +2230,16 @@
         <v>-0.227622</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.331425</v>
+        <v>0.326104</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.233692</v>
+        <v>-0.238756</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.166144</v>
+        <v>-0.167441</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.460389</v>
+        <v>-0.460632</v>
       </c>
     </row>
     <row r="30">
@@ -2511,58 +2511,58 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.779868</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.009364000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.237256</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.146239</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.253565</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.08444599999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.034008</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.06979</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.446108</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.15775</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.051389</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.083665</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.44105</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.258727</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.280844</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.085981</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.03469</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.008900999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2633,58 +2633,58 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.019</v>
+        <v>0.798868</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.030833</v>
+        <v>0.040197</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.014533</v>
+        <v>1.251789</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.042522</v>
+        <v>0.188761</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.031389</v>
+        <v>0.284954</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.043055</v>
+        <v>0.127501</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.022389</v>
+        <v>0.056397</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.013694</v>
+        <v>0.083484</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.023789</v>
+        <v>0.469897</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.028869</v>
+        <v>0.186619</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.022698</v>
+        <v>0.074087</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.044143</v>
+        <v>0.127808</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.44105</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.258727</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.320504</v>
+        <v>1.601348</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.073944</v>
+        <v>0.159925</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.097236</v>
+        <v>0.131926</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.215402</v>
+        <v>0.224303</v>
       </c>
     </row>
     <row r="37">
@@ -3365,58 +3365,58 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.780838</v>
+        <v>0.0009700000000000001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.010702</v>
+        <v>0.001338</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.238544</v>
+        <v>0.001288</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.150829</v>
+        <v>0.00459</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.257947</v>
+        <v>0.004382</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.084504</v>
+        <v>5.8e-05</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.036747</v>
+        <v>0.002739</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.06979</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.446108</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.15775</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.051389</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.106057</v>
+        <v>0.022392</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.472889</v>
+        <v>0.031839</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.2668</v>
+        <v>0.008073</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.28219</v>
+        <v>0.001346</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.086294</v>
+        <v>0.000313</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.036493</v>
+        <v>0.001803</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.008900999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8025,13 +8025,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003965</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.004413</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003724</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -8086,13 +8086,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003965</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.004413</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003724</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17920,7 +17920,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
@@ -28438,7 +28438,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -30666,7 +30670,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E215" s="5" t="n">
         <v>-0.003965</v>
       </c>
@@ -32898,7 +32906,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -34764,7 +34772,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -40512,7 +40520,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -41452,7 +41460,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -44084,7 +44092,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -45896,7 +45904,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -47814,7 +47822,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E379" s="5" t="n">

--- a/output/pdf_financials_xlsx/TRS.xlsx
+++ b/output/pdf_financials_xlsx/TRS.xlsx
@@ -7305,13 +7305,13 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.156566</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.061087</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -26766,7 +26766,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TRS.xlsx
+++ b/output/pdf_financials_xlsx/TRS.xlsx
@@ -1309,7 +1309,7 @@
         <v>-3.981457</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-1.710261</v>
+        <v>-1.608352</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-0.975394</v>
@@ -1370,7 +1370,7 @@
         <v>-0.25567</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.101909</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2072,7 +2072,7 @@
         <v>-4.04884</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.796743</v>
+        <v>-1.694834</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.978528</v>
@@ -2194,7 +2194,7 @@
         <v>-4.04884</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.790432</v>
+        <v>-1.688523</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.973261</v>
@@ -2352,7 +2352,7 @@
         <v>-6.421518554639672</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-6.336237341079565</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -7222,7 +7222,7 @@
         <v>0</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>0.038412</v>
       </c>
     </row>
     <row r="111">
@@ -7512,7 +7512,7 @@
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.129249</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
@@ -7521,13 +7521,13 @@
         <v>0</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.01868</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>0.01078</v>
       </c>
     </row>
     <row r="116">
@@ -19926,7 +19926,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -20964,7 +20968,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -23054,7 +23062,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -46120,7 +46132,11 @@
           <t>Future income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
